--- a/templates/Template_Escalonamento.xlsx
+++ b/templates/Template_Escalonamento.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Exemplo - Time Cloud" sheetId="1" r:id="rId1"/>
-    <sheet name="Exemplo - Matricial" sheetId="2" r:id="rId2"/>
+    <sheet name="DevOps - Cloud" sheetId="1" r:id="rId1"/>
+    <sheet name="Template Vazio" sheetId="2" r:id="rId2"/>
     <sheet name="Instruções" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
@@ -399,275 +399,198 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:AI15"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="2.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
-    <col min="4" max="4" width="2.83203125" customWidth="1"/>
+    <col min="1" max="1" width="32.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
     <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="2.83203125" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" customWidth="1"/>
-    <col min="8" max="8" width="2.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" customWidth="1"/>
     <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="2.83203125" customWidth="1"/>
-    <col min="11" max="11" width="8.83203125" customWidth="1"/>
-    <col min="12" max="12" width="2.83203125" customWidth="1"/>
-    <col min="13" max="13" width="2.83203125" customWidth="1"/>
-    <col min="14" max="14" width="2.83203125" customWidth="1"/>
-    <col min="15" max="15" width="2.83203125" customWidth="1"/>
-    <col min="16" max="16" width="30.83203125" customWidth="1"/>
-    <col min="17" max="17" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" customWidth="1"/>
+    <col min="15" max="15" width="12.83203125" customWidth="1"/>
+    <col min="16" max="16" width="12.83203125" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1"/>
+    <col min="18" max="18" width="12.83203125" customWidth="1"/>
+    <col min="19" max="19" width="12.83203125" customWidth="1"/>
+    <col min="20" max="20" width="12.83203125" customWidth="1"/>
+    <col min="21" max="21" width="12.83203125" customWidth="1"/>
+    <col min="22" max="22" width="12.83203125" customWidth="1"/>
+    <col min="23" max="23" width="12.83203125" customWidth="1"/>
+    <col min="24" max="24" width="12.83203125" customWidth="1"/>
+    <col min="25" max="25" width="12.83203125" customWidth="1"/>
+    <col min="26" max="26" width="12.83203125" customWidth="1"/>
+    <col min="27" max="27" width="12.83203125" customWidth="1"/>
+    <col min="28" max="28" width="12.83203125" customWidth="1"/>
+    <col min="29" max="29" width="12.83203125" customWidth="1"/>
+    <col min="30" max="30" width="12.83203125" customWidth="1"/>
+    <col min="31" max="31" width="12.83203125" customWidth="1"/>
+    <col min="32" max="32" width="12.83203125" customWidth="1"/>
+    <col min="33" max="33" width="12.83203125" customWidth="1"/>
+    <col min="34" max="34" width="12.83203125" customWidth="1"/>
+    <col min="35" max="35" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Nome</v>
-      </c>
-      <c r="B1" t="str">
-        <v/>
-      </c>
-      <c r="C1" t="str">
-        <v>Dia</v>
-      </c>
-      <c r="D1" t="str">
-        <v/>
-      </c>
-      <c r="E1" t="str">
-        <v>Data início</v>
-      </c>
-      <c r="F1" t="str">
-        <v/>
-      </c>
-      <c r="G1" t="str">
-        <v>Início</v>
-      </c>
-      <c r="H1" t="str">
-        <v/>
-      </c>
-      <c r="I1" t="str">
-        <v>Data fim</v>
-      </c>
-      <c r="J1" t="str">
-        <v/>
-      </c>
-      <c r="K1" t="str">
-        <v>Fim</v>
-      </c>
-      <c r="L1" t="str">
-        <v/>
-      </c>
-      <c r="M1" t="str">
-        <v/>
-      </c>
-      <c r="N1" t="str">
-        <v/>
-      </c>
-      <c r="O1" t="str">
-        <v/>
-      </c>
-      <c r="P1" t="str">
-        <v>Plantonistas</v>
-      </c>
-      <c r="Q1" t="str">
-        <v/>
+        <v>DevOps / Cloud</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>João Silva</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v>Terça</v>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v>01/jul</v>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v>18:00</v>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v>02/jul</v>
-      </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
-        <v>06:00</v>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v>JOÃO DA SILVA</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>11 99999-1111</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Maria Santos</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v>Quarta</v>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v>02/jul</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v>18:00</v>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>03/jul</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v>06:00</v>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
-        <v/>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3" t="str">
-        <v>MARIA DOS SANTOS</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>11 99999-2222</v>
+        <v>Julho/2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Pedro Costa</v>
+        <v>Colaborador</v>
       </c>
       <c r="B4" t="str">
-        <v/>
+        <v>Cargo</v>
       </c>
       <c r="C4" t="str">
-        <v>Quinta</v>
+        <v>Contato</v>
       </c>
       <c r="D4" t="str">
-        <v/>
+        <v>Nível</v>
       </c>
       <c r="E4" t="str">
-        <v>03/jul</v>
+        <v>01</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>02</v>
       </c>
       <c r="G4" t="str">
-        <v>18:00</v>
+        <v>03</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>04</v>
       </c>
       <c r="I4" t="str">
-        <v>04/jul</v>
+        <v>05</v>
       </c>
       <c r="J4" t="str">
-        <v/>
+        <v>06</v>
       </c>
       <c r="K4" t="str">
-        <v>06:00</v>
+        <v>07</v>
       </c>
       <c r="L4" t="str">
-        <v/>
+        <v>08</v>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>09</v>
       </c>
       <c r="N4" t="str">
-        <v/>
+        <v>10</v>
       </c>
       <c r="O4" t="str">
-        <v/>
+        <v>11</v>
       </c>
       <c r="P4" t="str">
-        <v>PEDRO HENRIQUE COSTA</v>
+        <v>12</v>
       </c>
       <c r="Q4" t="str">
-        <v>21 99999-3333</v>
+        <v>13</v>
+      </c>
+      <c r="R4" t="str">
+        <v>14</v>
+      </c>
+      <c r="S4" t="str">
+        <v>15</v>
+      </c>
+      <c r="T4" t="str">
+        <v>16</v>
+      </c>
+      <c r="U4" t="str">
+        <v>17</v>
+      </c>
+      <c r="V4" t="str">
+        <v>18</v>
+      </c>
+      <c r="W4" t="str">
+        <v>19</v>
+      </c>
+      <c r="X4" t="str">
+        <v>20</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>21</v>
+      </c>
+      <c r="Z4" t="str">
+        <v>22</v>
+      </c>
+      <c r="AA4" t="str">
+        <v>23</v>
+      </c>
+      <c r="AB4" t="str">
+        <v>24</v>
+      </c>
+      <c r="AC4" t="str">
+        <v>25</v>
+      </c>
+      <c r="AD4" t="str">
+        <v>26</v>
+      </c>
+      <c r="AE4" t="str">
+        <v>27</v>
+      </c>
+      <c r="AF4" t="str">
+        <v>28</v>
+      </c>
+      <c r="AG4" t="str">
+        <v>29</v>
+      </c>
+      <c r="AH4" t="str">
+        <v>30</v>
+      </c>
+      <c r="AI4" t="str">
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Ana Oliveira</v>
+        <v>Claudio Rogerio Ribeiro Lopes</v>
       </c>
       <c r="B5" t="str">
-        <v/>
+        <v>Analista DevOps III</v>
       </c>
       <c r="C5" t="str">
-        <v>Sexta</v>
+        <v>14 99137-1213</v>
       </c>
       <c r="D5" t="str">
-        <v/>
+        <v>1º Escalão</v>
       </c>
       <c r="E5" t="str">
-        <v>04/jul</v>
+        <v>18:00-06:00</v>
       </c>
       <c r="F5" t="str">
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>18:00</v>
+        <v/>
       </c>
       <c r="H5" t="str">
         <v/>
       </c>
       <c r="I5" t="str">
-        <v>05/jul</v>
+        <v/>
       </c>
       <c r="J5" t="str">
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>08:00</v>
+        <v/>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>18:00-06:00</v>
       </c>
       <c r="M5" t="str">
         <v/>
@@ -679,45 +602,87 @@
         <v/>
       </c>
       <c r="P5" t="str">
-        <v>ANA CAROLINA OLIVEIRA</v>
+        <v/>
       </c>
       <c r="Q5" t="str">
-        <v>11 99999-4444</v>
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
+      <c r="T5" t="str">
+        <v/>
+      </c>
+      <c r="U5" t="str">
+        <v/>
+      </c>
+      <c r="V5" t="str">
+        <v/>
+      </c>
+      <c r="W5" t="str">
+        <v/>
+      </c>
+      <c r="X5" t="str">
+        <v/>
+      </c>
+      <c r="Y5" t="str">
+        <v/>
+      </c>
+      <c r="Z5" t="str">
+        <v/>
+      </c>
+      <c r="AA5" t="str">
+        <v/>
+      </c>
+      <c r="AB5" t="str">
+        <v>18:00-06:00</v>
+      </c>
+      <c r="AC5" t="str">
+        <v/>
+      </c>
+      <c r="AD5" t="str">
+        <v/>
+      </c>
+      <c r="AE5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>João Silva</v>
+        <v>Vitor Morais Clauz</v>
       </c>
       <c r="B6" t="str">
-        <v/>
+        <v>Analista DevOps II</v>
       </c>
       <c r="C6" t="str">
-        <v>Sábado</v>
+        <v>11 98312-4847</v>
       </c>
       <c r="D6" t="str">
-        <v/>
+        <v>1º Escalão</v>
       </c>
       <c r="E6" t="str">
-        <v>05/jul</v>
+        <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>18:00-06:00</v>
       </c>
       <c r="G6" t="str">
-        <v>08:00</v>
+        <v/>
       </c>
       <c r="H6" t="str">
         <v/>
       </c>
       <c r="I6" t="str">
-        <v>06/jul</v>
+        <v/>
       </c>
       <c r="J6" t="str">
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>08:00</v>
+        <v>18:00-06:00</v>
       </c>
       <c r="L6" t="str">
         <v/>
@@ -732,45 +697,87 @@
         <v/>
       </c>
       <c r="P6" t="str">
-        <v>CARLOS EDUARDO LIMA</v>
+        <v/>
       </c>
       <c r="Q6" t="str">
-        <v>14 99999-5555</v>
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <v/>
+      </c>
+      <c r="S6" t="str">
+        <v>18:00-06:00</v>
+      </c>
+      <c r="T6" t="str">
+        <v/>
+      </c>
+      <c r="U6" t="str">
+        <v>08:00-06:00</v>
+      </c>
+      <c r="V6" t="str">
+        <v/>
+      </c>
+      <c r="W6" t="str">
+        <v>18:00-06:00</v>
+      </c>
+      <c r="X6" t="str">
+        <v/>
+      </c>
+      <c r="Y6" t="str">
+        <v/>
+      </c>
+      <c r="Z6" t="str">
+        <v/>
+      </c>
+      <c r="AA6" t="str">
+        <v/>
+      </c>
+      <c r="AB6" t="str">
+        <v/>
+      </c>
+      <c r="AC6" t="str">
+        <v>18:00-06:00</v>
+      </c>
+      <c r="AD6" t="str">
+        <v/>
+      </c>
+      <c r="AE6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Maria Santos</v>
+        <v>Vitor Fratucci Francisco</v>
       </c>
       <c r="B7" t="str">
-        <v/>
+        <v>Analista DevOps I</v>
       </c>
       <c r="C7" t="str">
-        <v>Domingo</v>
+        <v>11 99759-6678</v>
       </c>
       <c r="D7" t="str">
-        <v/>
+        <v>1º Escalão</v>
       </c>
       <c r="E7" t="str">
-        <v>06/jul</v>
+        <v/>
       </c>
       <c r="F7" t="str">
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>08:00</v>
+        <v>18:00-08:00</v>
       </c>
       <c r="H7" t="str">
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>07/jul</v>
+        <v/>
       </c>
       <c r="J7" t="str">
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>06:00</v>
+        <v/>
       </c>
       <c r="L7" t="str">
         <v/>
@@ -782,48 +789,90 @@
         <v/>
       </c>
       <c r="O7" t="str">
-        <v/>
+        <v>08:00-08:00</v>
       </c>
       <c r="P7" t="str">
         <v/>
       </c>
       <c r="Q7" t="str">
         <v/>
+      </c>
+      <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str">
+        <v/>
+      </c>
+      <c r="T7" t="str">
+        <v/>
+      </c>
+      <c r="U7" t="str">
+        <v/>
+      </c>
+      <c r="V7" t="str">
+        <v/>
+      </c>
+      <c r="W7" t="str">
+        <v/>
+      </c>
+      <c r="X7" t="str">
+        <v>18:00-08:00</v>
+      </c>
+      <c r="Y7" t="str">
+        <v/>
+      </c>
+      <c r="Z7" t="str">
+        <v/>
+      </c>
+      <c r="AA7" t="str">
+        <v/>
+      </c>
+      <c r="AB7" t="str">
+        <v/>
+      </c>
+      <c r="AC7" t="str">
+        <v/>
+      </c>
+      <c r="AD7" t="str">
+        <v/>
+      </c>
+      <c r="AE7" t="str">
+        <v>18:00-08:00</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Pedro Costa</v>
+        <v>David Alves de Araujo</v>
       </c>
       <c r="B8" t="str">
-        <v/>
+        <v>Analista DevOps III</v>
       </c>
       <c r="C8" t="str">
-        <v>Segunda</v>
+        <v>21 99834-0406</v>
       </c>
       <c r="D8" t="str">
-        <v/>
+        <v>1º Escalão</v>
       </c>
       <c r="E8" t="str">
-        <v>07/jul</v>
+        <v/>
       </c>
       <c r="F8" t="str">
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>18:00</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>24hs</v>
       </c>
       <c r="I8" t="str">
-        <v>08/jul</v>
+        <v/>
       </c>
       <c r="J8" t="str">
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>06:00</v>
+        <v/>
       </c>
       <c r="L8" t="str">
         <v/>
@@ -838,45 +887,87 @@
         <v/>
       </c>
       <c r="P8" t="str">
-        <v>Escalation</v>
+        <v/>
       </c>
       <c r="Q8" t="str">
+        <v>18:00-06:00</v>
+      </c>
+      <c r="R8" t="str">
+        <v/>
+      </c>
+      <c r="S8" t="str">
+        <v/>
+      </c>
+      <c r="T8" t="str">
+        <v/>
+      </c>
+      <c r="U8" t="str">
+        <v/>
+      </c>
+      <c r="V8" t="str">
+        <v>18:00-06:00</v>
+      </c>
+      <c r="W8" t="str">
+        <v/>
+      </c>
+      <c r="X8" t="str">
+        <v/>
+      </c>
+      <c r="Y8" t="str">
+        <v/>
+      </c>
+      <c r="Z8" t="str">
+        <v>08:00-06:00</v>
+      </c>
+      <c r="AA8" t="str">
+        <v/>
+      </c>
+      <c r="AB8" t="str">
+        <v/>
+      </c>
+      <c r="AC8" t="str">
+        <v/>
+      </c>
+      <c r="AD8" t="str">
+        <v/>
+      </c>
+      <c r="AE8" t="str">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Carlos Lima</v>
+        <v>Ricardo Fracini</v>
       </c>
       <c r="B9" t="str">
-        <v/>
+        <v>Analista DevOps II</v>
       </c>
       <c r="C9" t="str">
-        <v>Terça</v>
+        <v>11 96911-6690</v>
       </c>
       <c r="D9" t="str">
-        <v/>
+        <v>1º Escalão</v>
       </c>
       <c r="E9" t="str">
-        <v>08/jul</v>
+        <v/>
       </c>
       <c r="F9" t="str">
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>18:00</v>
+        <v/>
       </c>
       <c r="H9" t="str">
         <v/>
       </c>
       <c r="I9" t="str">
-        <v>09/jul</v>
+        <v>08:00-06:00</v>
       </c>
       <c r="J9" t="str">
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>06:00</v>
+        <v/>
       </c>
       <c r="L9" t="str">
         <v/>
@@ -885,51 +976,93 @@
         <v/>
       </c>
       <c r="N9" t="str">
-        <v/>
+        <v>18:00-08:00</v>
       </c>
       <c r="O9" t="str">
         <v/>
       </c>
       <c r="P9" t="str">
-        <v>1 - Gerente Fulano</v>
+        <v/>
       </c>
       <c r="Q9" t="str">
-        <v>11 99999-8888</v>
+        <v/>
+      </c>
+      <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str">
+        <v/>
+      </c>
+      <c r="T9" t="str">
+        <v>18:00-06:00</v>
+      </c>
+      <c r="U9" t="str">
+        <v/>
+      </c>
+      <c r="V9" t="str">
+        <v/>
+      </c>
+      <c r="W9" t="str">
+        <v/>
+      </c>
+      <c r="X9" t="str">
+        <v/>
+      </c>
+      <c r="Y9" t="str">
+        <v>08:00-08:00</v>
+      </c>
+      <c r="Z9" t="str">
+        <v/>
+      </c>
+      <c r="AA9" t="str">
+        <v/>
+      </c>
+      <c r="AB9" t="str">
+        <v/>
+      </c>
+      <c r="AC9" t="str">
+        <v/>
+      </c>
+      <c r="AD9" t="str">
+        <v/>
+      </c>
+      <c r="AE9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Ana Oliveira</v>
+        <v>Yago Castilho</v>
       </c>
       <c r="B10" t="str">
-        <v/>
+        <v>Analista DevOps</v>
       </c>
       <c r="C10" t="str">
-        <v>Quarta</v>
+        <v>11 93444-1518</v>
       </c>
       <c r="D10" t="str">
-        <v/>
+        <v>1º Escalão</v>
       </c>
       <c r="E10" t="str">
-        <v>09/jul</v>
+        <v/>
       </c>
       <c r="F10" t="str">
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>18:00</v>
+        <v/>
       </c>
       <c r="H10" t="str">
         <v/>
       </c>
       <c r="I10" t="str">
-        <v>10/jul</v>
+        <v/>
       </c>
       <c r="J10" t="str">
-        <v/>
+        <v>18:00-06:00</v>
       </c>
       <c r="K10" t="str">
-        <v>06:00</v>
+        <v/>
       </c>
       <c r="L10" t="str">
         <v/>
@@ -944,51 +1077,93 @@
         <v/>
       </c>
       <c r="P10" t="str">
-        <v>2 - Diretor Ciclano</v>
+        <v/>
       </c>
       <c r="Q10" t="str">
-        <v>11 99999-9999</v>
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v>18:00-06:00</v>
+      </c>
+      <c r="S10" t="str">
+        <v/>
+      </c>
+      <c r="T10" t="str">
+        <v/>
+      </c>
+      <c r="U10" t="str">
+        <v/>
+      </c>
+      <c r="V10" t="str">
+        <v>08:00-08:00</v>
+      </c>
+      <c r="W10" t="str">
+        <v/>
+      </c>
+      <c r="X10" t="str">
+        <v/>
+      </c>
+      <c r="Y10" t="str">
+        <v/>
+      </c>
+      <c r="Z10" t="str">
+        <v/>
+      </c>
+      <c r="AA10" t="str">
+        <v/>
+      </c>
+      <c r="AB10" t="str">
+        <v/>
+      </c>
+      <c r="AC10" t="str">
+        <v/>
+      </c>
+      <c r="AD10" t="str">
+        <v>18:00-06:00</v>
+      </c>
+      <c r="AE10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>João Silva</v>
+        <v>Marcelo Vilela de Morais</v>
       </c>
       <c r="B11" t="str">
-        <v/>
+        <v>Analista DevOps I</v>
       </c>
       <c r="C11" t="str">
-        <v>Quinta</v>
+        <v>11 98273-9488</v>
       </c>
       <c r="D11" t="str">
-        <v/>
+        <v>1º Escalão</v>
       </c>
       <c r="E11" t="str">
-        <v>10/jul</v>
+        <v/>
       </c>
       <c r="F11" t="str">
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>18:00</v>
+        <v/>
       </c>
       <c r="H11" t="str">
         <v/>
       </c>
       <c r="I11" t="str">
-        <v>11/jul</v>
+        <v/>
       </c>
       <c r="J11" t="str">
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>06:00</v>
+        <v/>
       </c>
       <c r="L11" t="str">
         <v/>
       </c>
       <c r="M11" t="str">
-        <v/>
+        <v>08:00-06:00</v>
       </c>
       <c r="N11" t="str">
         <v/>
@@ -997,251 +1172,519 @@
         <v/>
       </c>
       <c r="P11" t="str">
-        <v>3 - VP Beltrano</v>
+        <v>08:00-06:00</v>
       </c>
       <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v/>
+      </c>
+      <c r="S11" t="str">
+        <v/>
+      </c>
+      <c r="T11" t="str">
+        <v/>
+      </c>
+      <c r="U11" t="str">
+        <v/>
+      </c>
+      <c r="V11" t="str">
+        <v/>
+      </c>
+      <c r="W11" t="str">
+        <v/>
+      </c>
+      <c r="X11" t="str">
+        <v/>
+      </c>
+      <c r="Y11" t="str">
+        <v/>
+      </c>
+      <c r="Z11" t="str">
+        <v/>
+      </c>
+      <c r="AA11" t="str">
+        <v>18:00-06:00</v>
+      </c>
+      <c r="AB11" t="str">
+        <v/>
+      </c>
+      <c r="AC11" t="str">
+        <v/>
+      </c>
+      <c r="AD11" t="str">
+        <v/>
+      </c>
+      <c r="AE11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Leandro Silva</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Especialista</v>
+      </c>
+      <c r="C13" t="str">
+        <v>24 99266-6604</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2º Escalão</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <v/>
+      </c>
+      <c r="S13" t="str">
+        <v/>
+      </c>
+      <c r="T13" t="str">
+        <v/>
+      </c>
+      <c r="U13" t="str">
+        <v/>
+      </c>
+      <c r="V13" t="str">
+        <v/>
+      </c>
+      <c r="W13" t="str">
+        <v/>
+      </c>
+      <c r="X13" t="str">
+        <v/>
+      </c>
+      <c r="Y13" t="str">
+        <v/>
+      </c>
+      <c r="Z13" t="str">
+        <v/>
+      </c>
+      <c r="AA13" t="str">
+        <v/>
+      </c>
+      <c r="AB13" t="str">
+        <v/>
+      </c>
+      <c r="AC13" t="str">
+        <v/>
+      </c>
+      <c r="AD13" t="str">
+        <v/>
+      </c>
+      <c r="AE13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Jair Nascimento</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Coordenador</v>
+      </c>
+      <c r="C14" t="str">
+        <v>11 99741-1892</v>
+      </c>
+      <c r="D14" t="str">
+        <v>3º Escalão</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <v/>
+      </c>
+      <c r="S14" t="str">
+        <v/>
+      </c>
+      <c r="T14" t="str">
+        <v/>
+      </c>
+      <c r="U14" t="str">
+        <v/>
+      </c>
+      <c r="V14" t="str">
+        <v/>
+      </c>
+      <c r="W14" t="str">
+        <v/>
+      </c>
+      <c r="X14" t="str">
+        <v/>
+      </c>
+      <c r="Y14" t="str">
+        <v/>
+      </c>
+      <c r="Z14" t="str">
+        <v/>
+      </c>
+      <c r="AA14" t="str">
+        <v/>
+      </c>
+      <c r="AB14" t="str">
+        <v/>
+      </c>
+      <c r="AC14" t="str">
+        <v/>
+      </c>
+      <c r="AD14" t="str">
+        <v/>
+      </c>
+      <c r="AE14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Alex Almeida</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Gerente</v>
+      </c>
+      <c r="C15" t="str">
+        <v>11 99693-6308</v>
+      </c>
+      <c r="D15" t="str">
+        <v>4º Escalão</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15" t="str">
+        <v/>
+      </c>
+      <c r="T15" t="str">
+        <v/>
+      </c>
+      <c r="U15" t="str">
+        <v/>
+      </c>
+      <c r="V15" t="str">
+        <v/>
+      </c>
+      <c r="W15" t="str">
+        <v/>
+      </c>
+      <c r="X15" t="str">
+        <v/>
+      </c>
+      <c r="Y15" t="str">
+        <v/>
+      </c>
+      <c r="Z15" t="str">
+        <v/>
+      </c>
+      <c r="AA15" t="str">
+        <v/>
+      </c>
+      <c r="AB15" t="str">
+        <v/>
+      </c>
+      <c r="AC15" t="str">
+        <v/>
+      </c>
+      <c r="AD15" t="str">
+        <v/>
+      </c>
+      <c r="AE15" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AI15"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:AI9"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="2.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
-    <col min="12" max="12" width="14.83203125" customWidth="1"/>
-    <col min="13" max="13" width="14.83203125" customWidth="1"/>
-    <col min="14" max="14" width="14.83203125" customWidth="1"/>
-    <col min="15" max="15" width="14.83203125" customWidth="1"/>
-    <col min="16" max="16" width="14.83203125" customWidth="1"/>
-    <col min="17" max="17" width="14.83203125" customWidth="1"/>
-    <col min="18" max="18" width="14.83203125" customWidth="1"/>
-    <col min="19" max="19" width="14.83203125" customWidth="1"/>
-    <col min="20" max="20" width="14.83203125" customWidth="1"/>
+    <col min="1" max="1" width="32.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" customWidth="1"/>
+    <col min="15" max="15" width="12.83203125" customWidth="1"/>
+    <col min="16" max="16" width="12.83203125" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1"/>
+    <col min="18" max="18" width="12.83203125" customWidth="1"/>
+    <col min="19" max="19" width="12.83203125" customWidth="1"/>
+    <col min="20" max="20" width="12.83203125" customWidth="1"/>
+    <col min="21" max="21" width="12.83203125" customWidth="1"/>
+    <col min="22" max="22" width="12.83203125" customWidth="1"/>
+    <col min="23" max="23" width="12.83203125" customWidth="1"/>
+    <col min="24" max="24" width="12.83203125" customWidth="1"/>
+    <col min="25" max="25" width="12.83203125" customWidth="1"/>
+    <col min="26" max="26" width="12.83203125" customWidth="1"/>
+    <col min="27" max="27" width="12.83203125" customWidth="1"/>
+    <col min="28" max="28" width="12.83203125" customWidth="1"/>
+    <col min="29" max="29" width="12.83203125" customWidth="1"/>
+    <col min="30" max="30" width="12.83203125" customWidth="1"/>
+    <col min="31" max="31" width="12.83203125" customWidth="1"/>
+    <col min="32" max="32" width="12.83203125" customWidth="1"/>
+    <col min="33" max="33" width="12.83203125" customWidth="1"/>
+    <col min="34" max="34" width="12.83203125" customWidth="1"/>
+    <col min="35" max="35" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>ÁREA EXEMPLO - INFRAESTRUTURA</v>
+        <v>NOME DA ÁREA AQUI</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Colaborador</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Cargo</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Nível</v>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v>Contato</v>
-      </c>
-      <c r="F2" t="str">
-        <v>1</v>
-      </c>
-      <c r="G2" t="str">
-        <v>2</v>
-      </c>
-      <c r="H2" t="str">
-        <v>3</v>
-      </c>
-      <c r="I2" t="str">
-        <v>4</v>
-      </c>
-      <c r="J2" t="str">
-        <v>5</v>
-      </c>
-      <c r="K2" t="str">
-        <v>6</v>
-      </c>
-      <c r="L2" t="str">
-        <v>7</v>
-      </c>
-      <c r="M2" t="str">
-        <v>8</v>
-      </c>
-      <c r="N2" t="str">
-        <v>9</v>
-      </c>
-      <c r="O2" t="str">
-        <v>10</v>
-      </c>
-      <c r="P2" t="str">
-        <v>11</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>12</v>
-      </c>
-      <c r="R2" t="str">
-        <v>13</v>
-      </c>
-      <c r="S2" t="str">
-        <v>14</v>
-      </c>
-      <c r="T2" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>João Silva</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Analista SR</v>
-      </c>
-      <c r="C3" t="str">
-        <v>1º Escalão</v>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v>11 99999-1111</v>
-      </c>
-      <c r="F3" t="str">
-        <v>18:00 às 06:00</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>18:00 às 06:00</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
-        <v>18:00 às 06:00</v>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3" t="str">
-        <v/>
-      </c>
-      <c r="Q3" t="str">
-        <v/>
-      </c>
-      <c r="R3" t="str">
-        <v>18:00 às 06:00</v>
-      </c>
-      <c r="S3" t="str">
-        <v/>
-      </c>
-      <c r="T3" t="str">
-        <v/>
+        <v>Mês/Ano (ex: Agosto/2026)</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Maria Santos</v>
+        <v>Colaborador</v>
       </c>
       <c r="B4" t="str">
-        <v>Analista PL</v>
+        <v>Cargo</v>
       </c>
       <c r="C4" t="str">
-        <v>1º Escalão</v>
+        <v>Contato</v>
       </c>
       <c r="D4" t="str">
-        <v/>
+        <v>Nível</v>
       </c>
       <c r="E4" t="str">
-        <v>11 99999-2222</v>
+        <v>01</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>02</v>
       </c>
       <c r="G4" t="str">
-        <v>18:00 às 06:00</v>
+        <v>03</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>04</v>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>05</v>
       </c>
       <c r="J4" t="str">
-        <v>18:00 às 06:00</v>
+        <v>06</v>
       </c>
       <c r="K4" t="str">
-        <v/>
+        <v>07</v>
       </c>
       <c r="L4" t="str">
-        <v/>
+        <v>08</v>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>09</v>
       </c>
       <c r="N4" t="str">
-        <v>18:00 às 06:00</v>
+        <v>10</v>
       </c>
       <c r="O4" t="str">
-        <v/>
+        <v>11</v>
       </c>
       <c r="P4" t="str">
-        <v/>
+        <v>12</v>
       </c>
       <c r="Q4" t="str">
-        <v/>
+        <v>13</v>
       </c>
       <c r="R4" t="str">
-        <v/>
+        <v>14</v>
       </c>
       <c r="S4" t="str">
-        <v>18:00 às 06:00</v>
+        <v>15</v>
       </c>
       <c r="T4" t="str">
-        <v/>
+        <v>16</v>
+      </c>
+      <c r="U4" t="str">
+        <v>17</v>
+      </c>
+      <c r="V4" t="str">
+        <v>18</v>
+      </c>
+      <c r="W4" t="str">
+        <v>19</v>
+      </c>
+      <c r="X4" t="str">
+        <v>20</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>21</v>
+      </c>
+      <c r="Z4" t="str">
+        <v>22</v>
+      </c>
+      <c r="AA4" t="str">
+        <v>23</v>
+      </c>
+      <c r="AB4" t="str">
+        <v>24</v>
+      </c>
+      <c r="AC4" t="str">
+        <v>25</v>
+      </c>
+      <c r="AD4" t="str">
+        <v>26</v>
+      </c>
+      <c r="AE4" t="str">
+        <v>27</v>
+      </c>
+      <c r="AF4" t="str">
+        <v>28</v>
+      </c>
+      <c r="AG4" t="str">
+        <v>29</v>
+      </c>
+      <c r="AH4" t="str">
+        <v>30</v>
+      </c>
+      <c r="AI4" t="str">
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Pedro Costa</v>
+        <v/>
       </c>
       <c r="B5" t="str">
-        <v>Analista JR</v>
+        <v/>
       </c>
       <c r="C5" t="str">
-        <v>2º Escalão</v>
+        <v/>
       </c>
       <c r="D5" t="str">
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>21 99999-3333</v>
+        <v/>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -1250,7 +1693,7 @@
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>18:00 às 06:00</v>
+        <v/>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -1259,7 +1702,7 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>08:00 às 08:00</v>
+        <v/>
       </c>
       <c r="L5" t="str">
         <v/>
@@ -1271,13 +1714,13 @@
         <v/>
       </c>
       <c r="O5" t="str">
-        <v>18:00 às 06:00</v>
+        <v/>
       </c>
       <c r="P5" t="str">
         <v/>
       </c>
       <c r="Q5" t="str">
-        <v>24hs</v>
+        <v/>
       </c>
       <c r="R5" t="str">
         <v/>
@@ -1286,24 +1729,69 @@
         <v/>
       </c>
       <c r="T5" t="str">
+        <v/>
+      </c>
+      <c r="U5" t="str">
+        <v/>
+      </c>
+      <c r="V5" t="str">
+        <v/>
+      </c>
+      <c r="W5" t="str">
+        <v/>
+      </c>
+      <c r="X5" t="str">
+        <v/>
+      </c>
+      <c r="Y5" t="str">
+        <v/>
+      </c>
+      <c r="Z5" t="str">
+        <v/>
+      </c>
+      <c r="AA5" t="str">
+        <v/>
+      </c>
+      <c r="AB5" t="str">
+        <v/>
+      </c>
+      <c r="AC5" t="str">
+        <v/>
+      </c>
+      <c r="AD5" t="str">
+        <v/>
+      </c>
+      <c r="AE5" t="str">
+        <v/>
+      </c>
+      <c r="AF5" t="str">
+        <v/>
+      </c>
+      <c r="AG5" t="str">
+        <v/>
+      </c>
+      <c r="AH5" t="str">
+        <v/>
+      </c>
+      <c r="AI5" t="str">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Ana Oliveira</v>
+        <v/>
       </c>
       <c r="B6" t="str">
-        <v>Especialista</v>
+        <v/>
       </c>
       <c r="C6" t="str">
-        <v>1º Escalão</v>
+        <v/>
       </c>
       <c r="D6" t="str">
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>11 99999-4444</v>
+        <v/>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -1324,7 +1812,7 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>08:00 às 08:00</v>
+        <v/>
       </c>
       <c r="M6" t="str">
         <v/>
@@ -1336,7 +1824,7 @@
         <v/>
       </c>
       <c r="P6" t="str">
-        <v>18:00 às 06:00</v>
+        <v/>
       </c>
       <c r="Q6" t="str">
         <v/>
@@ -1348,24 +1836,69 @@
         <v/>
       </c>
       <c r="T6" t="str">
-        <v>18:00 às 06:00</v>
+        <v/>
+      </c>
+      <c r="U6" t="str">
+        <v/>
+      </c>
+      <c r="V6" t="str">
+        <v/>
+      </c>
+      <c r="W6" t="str">
+        <v/>
+      </c>
+      <c r="X6" t="str">
+        <v/>
+      </c>
+      <c r="Y6" t="str">
+        <v/>
+      </c>
+      <c r="Z6" t="str">
+        <v/>
+      </c>
+      <c r="AA6" t="str">
+        <v/>
+      </c>
+      <c r="AB6" t="str">
+        <v/>
+      </c>
+      <c r="AC6" t="str">
+        <v/>
+      </c>
+      <c r="AD6" t="str">
+        <v/>
+      </c>
+      <c r="AE6" t="str">
+        <v/>
+      </c>
+      <c r="AF6" t="str">
+        <v/>
+      </c>
+      <c r="AG6" t="str">
+        <v/>
+      </c>
+      <c r="AH6" t="str">
+        <v/>
+      </c>
+      <c r="AI6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Carlos Lima</v>
+        <v/>
       </c>
       <c r="B7" t="str">
-        <v>Coordenador</v>
+        <v/>
       </c>
       <c r="C7" t="str">
-        <v>2º Escalão</v>
+        <v/>
       </c>
       <c r="D7" t="str">
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>14 99999-5555</v>
+        <v/>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -1410,422 +1943,475 @@
         <v/>
       </c>
       <c r="T7" t="str">
+        <v/>
+      </c>
+      <c r="U7" t="str">
+        <v/>
+      </c>
+      <c r="V7" t="str">
+        <v/>
+      </c>
+      <c r="W7" t="str">
+        <v/>
+      </c>
+      <c r="X7" t="str">
+        <v/>
+      </c>
+      <c r="Y7" t="str">
+        <v/>
+      </c>
+      <c r="Z7" t="str">
+        <v/>
+      </c>
+      <c r="AA7" t="str">
+        <v/>
+      </c>
+      <c r="AB7" t="str">
+        <v/>
+      </c>
+      <c r="AC7" t="str">
+        <v/>
+      </c>
+      <c r="AD7" t="str">
+        <v/>
+      </c>
+      <c r="AE7" t="str">
+        <v/>
+      </c>
+      <c r="AF7" t="str">
+        <v/>
+      </c>
+      <c r="AG7" t="str">
+        <v/>
+      </c>
+      <c r="AH7" t="str">
+        <v/>
+      </c>
+      <c r="AI7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v/>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
+        <v/>
+      </c>
+      <c r="S8" t="str">
+        <v/>
+      </c>
+      <c r="T8" t="str">
+        <v/>
+      </c>
+      <c r="U8" t="str">
+        <v/>
+      </c>
+      <c r="V8" t="str">
+        <v/>
+      </c>
+      <c r="W8" t="str">
+        <v/>
+      </c>
+      <c r="X8" t="str">
+        <v/>
+      </c>
+      <c r="Y8" t="str">
+        <v/>
+      </c>
+      <c r="Z8" t="str">
+        <v/>
+      </c>
+      <c r="AA8" t="str">
+        <v/>
+      </c>
+      <c r="AB8" t="str">
+        <v/>
+      </c>
+      <c r="AC8" t="str">
+        <v/>
+      </c>
+      <c r="AD8" t="str">
+        <v/>
+      </c>
+      <c r="AE8" t="str">
+        <v/>
+      </c>
+      <c r="AF8" t="str">
+        <v/>
+      </c>
+      <c r="AG8" t="str">
+        <v/>
+      </c>
+      <c r="AH8" t="str">
+        <v/>
+      </c>
+      <c r="AI8" t="str">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ÁREA EXEMPLO - CLOUD</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Colaborador</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Cargo</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Nível</v>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10" t="str">
-        <v>Contato</v>
-      </c>
-      <c r="F10" t="str">
-        <v>1</v>
-      </c>
-      <c r="G10" t="str">
-        <v>2</v>
-      </c>
-      <c r="H10" t="str">
-        <v>3</v>
-      </c>
-      <c r="I10" t="str">
-        <v>4</v>
-      </c>
-      <c r="J10" t="str">
-        <v>5</v>
-      </c>
-      <c r="K10" t="str">
-        <v>6</v>
-      </c>
-      <c r="L10" t="str">
-        <v>7</v>
-      </c>
-      <c r="M10" t="str">
-        <v>8</v>
-      </c>
-      <c r="N10" t="str">
-        <v>9</v>
-      </c>
-      <c r="O10" t="str">
-        <v>10</v>
-      </c>
-      <c r="P10" t="str">
-        <v>11</v>
-      </c>
-      <c r="Q10" t="str">
-        <v>12</v>
-      </c>
-      <c r="R10" t="str">
-        <v>13</v>
-      </c>
-      <c r="S10" t="str">
-        <v>14</v>
-      </c>
-      <c r="T10" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Lucas Ferreira</v>
-      </c>
-      <c r="B11" t="str">
-        <v>DevOps SR</v>
-      </c>
-      <c r="C11" t="str">
-        <v>1º Escalão</v>
-      </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11" t="str">
-        <v>11 99999-6666</v>
-      </c>
-      <c r="F11" t="str">
-        <v>18:00 às 06:00</v>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v>18:00 às 06:00</v>
-      </c>
-      <c r="I11" t="str">
-        <v/>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v>08:00 às 08:00</v>
-      </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
-      <c r="M11" t="str">
-        <v>18:00 às 06:00</v>
-      </c>
-      <c r="N11" t="str">
-        <v/>
-      </c>
-      <c r="O11" t="str">
-        <v/>
-      </c>
-      <c r="P11" t="str">
-        <v/>
-      </c>
-      <c r="Q11" t="str">
-        <v/>
-      </c>
-      <c r="R11" t="str">
-        <v>18:00 às 06:00</v>
-      </c>
-      <c r="S11" t="str">
-        <v/>
-      </c>
-      <c r="T11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Bruna Almeida</v>
-      </c>
-      <c r="B12" t="str">
-        <v>SRE</v>
-      </c>
-      <c r="C12" t="str">
-        <v>1º Escalão</v>
-      </c>
-      <c r="D12" t="str">
-        <v/>
-      </c>
-      <c r="E12" t="str">
-        <v>11 99999-7777</v>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v>18:00 às 06:00</v>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>18:00 às 06:00</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>08:00 às 08:00</v>
-      </c>
-      <c r="M12" t="str">
-        <v/>
-      </c>
-      <c r="N12" t="str">
-        <v>18:00 às 06:00</v>
-      </c>
-      <c r="O12" t="str">
-        <v/>
-      </c>
-      <c r="P12" t="str">
-        <v/>
-      </c>
-      <c r="Q12" t="str">
-        <v/>
-      </c>
-      <c r="R12" t="str">
-        <v/>
-      </c>
-      <c r="S12" t="str">
-        <v>18:00 às 06:00</v>
-      </c>
-      <c r="T12" t="str">
+        <v/>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str">
+        <v/>
+      </c>
+      <c r="T9" t="str">
+        <v/>
+      </c>
+      <c r="U9" t="str">
+        <v/>
+      </c>
+      <c r="V9" t="str">
+        <v/>
+      </c>
+      <c r="W9" t="str">
+        <v/>
+      </c>
+      <c r="X9" t="str">
+        <v/>
+      </c>
+      <c r="Y9" t="str">
+        <v/>
+      </c>
+      <c r="Z9" t="str">
+        <v/>
+      </c>
+      <c r="AA9" t="str">
+        <v/>
+      </c>
+      <c r="AB9" t="str">
+        <v/>
+      </c>
+      <c r="AC9" t="str">
+        <v/>
+      </c>
+      <c r="AD9" t="str">
+        <v/>
+      </c>
+      <c r="AE9" t="str">
+        <v/>
+      </c>
+      <c r="AF9" t="str">
+        <v/>
+      </c>
+      <c r="AG9" t="str">
+        <v/>
+      </c>
+      <c r="AH9" t="str">
+        <v/>
+      </c>
+      <c r="AI9" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AI9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A53"/>
+  <dimension ref="A1:A45"/>
   <cols>
-    <col min="1" max="1" width="100.83203125" customWidth="1"/>
+    <col min="1" max="1" width="90.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>INSTRUÇÕES DE PREENCHIMENTO</v>
+        <v>INSTRUÇÕES DE PREENCHIMENTO — Template de Escalonamento</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>O sistema aceita dois formatos de planilha para importação de escalas de sobreaviso:</v>
+        <v>ESTRUTURA DO ARQUIVO:</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>• Cada aba do Excel = uma área/departamento</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>FORMATO 1: TABULAR (Time Cloud)</v>
+        <v>• O nome da aba identifica a área (ex: "DevOps - Cloud", "PDV", "Redes")</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
+        <v>ESTRUTURA DA ABA:</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>• Linha 1: Nome da área (será usado para identificar no sistema)</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Cada linha representa um turno de sobreaviso. Colunas obrigatórias:</v>
+        <v>• Linha 2: Mês/Ano de referência (ex: "Julho/2026", "Agosto/2026")</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v xml:space="preserve">  • Nome — Nome curto do plantonista (ex: "João Silva")</v>
+        <v>• Linha 3: Vazia (separador)</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v xml:space="preserve">  • Dia — Dia da semana (opcional, apenas informativo)</v>
+        <v>• Linha 4: Cabeçalhos — Colaborador | Cargo | Contato | Nível | 01 | 02 | ... | 31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v xml:space="preserve">  • Data início — Data de início no formato DD/mês (ex: "01/jul", "15/ago")</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v xml:space="preserve">  • Início — Horário de início (ex: "18:00", "08:00")</v>
+        <v>• Linhas 5+: Dados dos plantonistas</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v xml:space="preserve">  • Data fim — Data de fim no formato DD/mês (ex: "02/jul")</v>
+        <v>COLUNAS FIXAS:</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v xml:space="preserve">  • Fim — Horário de fim (ex: "06:00", "08:00")</v>
+        <v>• Colaborador — Nome completo do plantonista</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>• Cargo — Ex: "Analista DevOps III", "Coordenador"</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Seção lateral "Plantonistas" (opcional mas recomendado):</v>
+        <v>• Contato — Telefone com DDD (ex: "11 98312-4847")</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v xml:space="preserve">  • Nome completo em MAIÚSCULAS + Telefone de contato na coluna ao lado</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v xml:space="preserve">  • O sistema associa automaticamente "Vitor Clauz" → "VITOR MORAIS CLAUZ" → "11 98312-4847"</v>
+        <v>• Nível — "1º Escalão", "2º Escalão", "3º Escalão", "4º Escalão" ou "Direto"</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>COLUNAS DE DIAS (01 a 31):</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Seção lateral "Escalation" (opcional):</v>
+        <v>• Preencher com o horário do sobreaviso naquele dia</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v xml:space="preserve">  • Formato: "1 - Nome do Gestor" + telefone na coluna ao lado</v>
+        <v>• Formatos aceitos:</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v xml:space="preserve">  • Define a cadeia de escalonamento para alertas não atendidos</v>
+        <v xml:space="preserve">    - "18:00-06:00" (horário início - horário fim)</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v xml:space="preserve">    - "18:00 às 06:00" (com "às")</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Veja a aba "Exemplo - Time Cloud" para referência.</v>
+        <v xml:space="preserve">    - "08:00-08:00" (turno de 24h)</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v xml:space="preserve">    - "24hs" ou "24h" (turno integral)</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
+        <v xml:space="preserve">    - "X" ou "S" (marca presença como 24h)</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>FORMATO 2: MATRICIAL (uma linha por colaborador, colunas = dias)</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
+        <v xml:space="preserve">    - Vazio = sem plantão nesse dia</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>REGRAS DE IMPORTAÇÃO:</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Estrutura:</v>
+        <v>• A importação SUBSTITUI toda a escala do mês para a área</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v xml:space="preserve">  • Linha de cabeçalho de área: Nome da área em MAIÚSCULAS (sozinha na linha)</v>
+        <v>• Plantonistas novos são criados automaticamente (senha padrão: plantonista123)</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v xml:space="preserve">  • Linha de colunas: Colaborador | Cargo | Nível | (vazio) | Contato | 1 | 2 | 3 | ... | 31</v>
+        <v>• Plantonistas existentes são atualizados (cargo, contato)</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v xml:space="preserve">  • Linhas de dados: Nome, cargo, nível, contato, e horários nos dias correspondentes</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>Formatos aceitos nos dias:</v>
+        <v>• Conflitos são detectados (mesmo plantonista em dois turnos sobrepostos)</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>• Níveis 2º, 3º, 4º não precisam ter dias preenchidos (são escalação fixa)</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v xml:space="preserve">  • "18:00 às 06:00" — turno com horário específico</v>
+        <v>MÚLTIPLAS ÁREAS:</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v xml:space="preserve">  • "08:00 às 08:00" — turno de 24h</v>
+        <v>• Crie uma aba para cada área no mesmo arquivo</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v xml:space="preserve">  • "24hs" ou "24h" — turno de 24h</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v xml:space="preserve">  • "X" ou "S" — marca presença (será interpretado como turno 24h)</v>
+        <v>• Ou envie arquivos separados por área</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v xml:space="preserve">  • Vazio — sem plantão nesse dia</v>
+        <v>DICAS:</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>• Não use proteção por senha no arquivo</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Veja a aba "Exemplo - Matricial" para referência.</v>
+        <v>• Aceita formatos .xlsx e .csv</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>• O sistema valida os dados antes de importar</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>DICAS</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>• O arquivo pode ser .xlsx ou .csv</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>• Cada aba do Excel pode representar uma área diferente (o nome da aba vira o nome da área)</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>• Se o Excel tiver senha/proteção, remova antes de importar</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>• Use a mesma escrita do nome em todas as ocorrências para o mapeamento funcionar</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>• Após importar, os colaboradores são criados automaticamente com senha padrão "plantonista123"</v>
+        <v>• Veja a aba "DevOps - Cloud" como exemplo preenchido</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A53"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A45"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/templates/Template_Escalonamento.xlsx
+++ b/templates/Template_Escalonamento.xlsx
@@ -401,41 +401,41 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AI15"/>
   <cols>
-    <col min="1" max="1" width="32.83203125" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
-    <col min="13" max="13" width="12.83203125" customWidth="1"/>
-    <col min="14" max="14" width="12.83203125" customWidth="1"/>
-    <col min="15" max="15" width="12.83203125" customWidth="1"/>
-    <col min="16" max="16" width="12.83203125" customWidth="1"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1"/>
-    <col min="18" max="18" width="12.83203125" customWidth="1"/>
-    <col min="19" max="19" width="12.83203125" customWidth="1"/>
-    <col min="20" max="20" width="12.83203125" customWidth="1"/>
-    <col min="21" max="21" width="12.83203125" customWidth="1"/>
-    <col min="22" max="22" width="12.83203125" customWidth="1"/>
-    <col min="23" max="23" width="12.83203125" customWidth="1"/>
-    <col min="24" max="24" width="12.83203125" customWidth="1"/>
-    <col min="25" max="25" width="12.83203125" customWidth="1"/>
-    <col min="26" max="26" width="12.83203125" customWidth="1"/>
-    <col min="27" max="27" width="12.83203125" customWidth="1"/>
-    <col min="28" max="28" width="12.83203125" customWidth="1"/>
-    <col min="29" max="29" width="12.83203125" customWidth="1"/>
-    <col min="30" max="30" width="12.83203125" customWidth="1"/>
-    <col min="31" max="31" width="12.83203125" customWidth="1"/>
-    <col min="32" max="32" width="12.83203125" customWidth="1"/>
-    <col min="33" max="33" width="12.83203125" customWidth="1"/>
-    <col min="34" max="34" width="12.83203125" customWidth="1"/>
-    <col min="35" max="35" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="35.83203125" customWidth="1"/>
+    <col min="2" max="2" width="25.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" customWidth="1"/>
+    <col min="6" max="6" width="13.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" customWidth="1"/>
+    <col min="10" max="10" width="13.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" customWidth="1"/>
+    <col min="12" max="12" width="13.83203125" customWidth="1"/>
+    <col min="13" max="13" width="13.83203125" customWidth="1"/>
+    <col min="14" max="14" width="13.83203125" customWidth="1"/>
+    <col min="15" max="15" width="13.83203125" customWidth="1"/>
+    <col min="16" max="16" width="13.83203125" customWidth="1"/>
+    <col min="17" max="17" width="13.83203125" customWidth="1"/>
+    <col min="18" max="18" width="13.83203125" customWidth="1"/>
+    <col min="19" max="19" width="13.83203125" customWidth="1"/>
+    <col min="20" max="20" width="13.83203125" customWidth="1"/>
+    <col min="21" max="21" width="13.83203125" customWidth="1"/>
+    <col min="22" max="22" width="13.83203125" customWidth="1"/>
+    <col min="23" max="23" width="13.83203125" customWidth="1"/>
+    <col min="24" max="24" width="13.83203125" customWidth="1"/>
+    <col min="25" max="25" width="13.83203125" customWidth="1"/>
+    <col min="26" max="26" width="13.83203125" customWidth="1"/>
+    <col min="27" max="27" width="13.83203125" customWidth="1"/>
+    <col min="28" max="28" width="13.83203125" customWidth="1"/>
+    <col min="29" max="29" width="13.83203125" customWidth="1"/>
+    <col min="30" max="30" width="13.83203125" customWidth="1"/>
+    <col min="31" max="31" width="13.83203125" customWidth="1"/>
+    <col min="32" max="32" width="13.83203125" customWidth="1"/>
+    <col min="33" max="33" width="13.83203125" customWidth="1"/>
+    <col min="34" max="34" width="13.83203125" customWidth="1"/>
+    <col min="35" max="35" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Julho/2026</v>
+        <v>Mês/Ano: (Selecione o mês correto direto no painel do sistema)</v>
       </c>
     </row>
     <row r="4">
@@ -1516,41 +1516,41 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AI9"/>
   <cols>
-    <col min="1" max="1" width="32.83203125" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
-    <col min="13" max="13" width="12.83203125" customWidth="1"/>
-    <col min="14" max="14" width="12.83203125" customWidth="1"/>
-    <col min="15" max="15" width="12.83203125" customWidth="1"/>
-    <col min="16" max="16" width="12.83203125" customWidth="1"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1"/>
-    <col min="18" max="18" width="12.83203125" customWidth="1"/>
-    <col min="19" max="19" width="12.83203125" customWidth="1"/>
-    <col min="20" max="20" width="12.83203125" customWidth="1"/>
-    <col min="21" max="21" width="12.83203125" customWidth="1"/>
-    <col min="22" max="22" width="12.83203125" customWidth="1"/>
-    <col min="23" max="23" width="12.83203125" customWidth="1"/>
-    <col min="24" max="24" width="12.83203125" customWidth="1"/>
-    <col min="25" max="25" width="12.83203125" customWidth="1"/>
-    <col min="26" max="26" width="12.83203125" customWidth="1"/>
-    <col min="27" max="27" width="12.83203125" customWidth="1"/>
-    <col min="28" max="28" width="12.83203125" customWidth="1"/>
-    <col min="29" max="29" width="12.83203125" customWidth="1"/>
-    <col min="30" max="30" width="12.83203125" customWidth="1"/>
-    <col min="31" max="31" width="12.83203125" customWidth="1"/>
-    <col min="32" max="32" width="12.83203125" customWidth="1"/>
-    <col min="33" max="33" width="12.83203125" customWidth="1"/>
-    <col min="34" max="34" width="12.83203125" customWidth="1"/>
-    <col min="35" max="35" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="35.83203125" customWidth="1"/>
+    <col min="2" max="2" width="25.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" customWidth="1"/>
+    <col min="6" max="6" width="13.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" customWidth="1"/>
+    <col min="10" max="10" width="13.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" customWidth="1"/>
+    <col min="12" max="12" width="13.83203125" customWidth="1"/>
+    <col min="13" max="13" width="13.83203125" customWidth="1"/>
+    <col min="14" max="14" width="13.83203125" customWidth="1"/>
+    <col min="15" max="15" width="13.83203125" customWidth="1"/>
+    <col min="16" max="16" width="13.83203125" customWidth="1"/>
+    <col min="17" max="17" width="13.83203125" customWidth="1"/>
+    <col min="18" max="18" width="13.83203125" customWidth="1"/>
+    <col min="19" max="19" width="13.83203125" customWidth="1"/>
+    <col min="20" max="20" width="13.83203125" customWidth="1"/>
+    <col min="21" max="21" width="13.83203125" customWidth="1"/>
+    <col min="22" max="22" width="13.83203125" customWidth="1"/>
+    <col min="23" max="23" width="13.83203125" customWidth="1"/>
+    <col min="24" max="24" width="13.83203125" customWidth="1"/>
+    <col min="25" max="25" width="13.83203125" customWidth="1"/>
+    <col min="26" max="26" width="13.83203125" customWidth="1"/>
+    <col min="27" max="27" width="13.83203125" customWidth="1"/>
+    <col min="28" max="28" width="13.83203125" customWidth="1"/>
+    <col min="29" max="29" width="13.83203125" customWidth="1"/>
+    <col min="30" max="30" width="13.83203125" customWidth="1"/>
+    <col min="31" max="31" width="13.83203125" customWidth="1"/>
+    <col min="32" max="32" width="13.83203125" customWidth="1"/>
+    <col min="33" max="33" width="13.83203125" customWidth="1"/>
+    <col min="34" max="34" width="13.83203125" customWidth="1"/>
+    <col min="35" max="35" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1560,7 +1560,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Mês/Ano (ex: Agosto/2026)</v>
+        <v>Mês/Ano: (Selecione o mês correto direto no painel do sistema antes de importar)</v>
       </c>
     </row>
     <row r="4">
@@ -2214,7 +2214,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A45"/>
+  <dimension ref="A1:A34"/>
   <cols>
     <col min="1" max="1" width="90.83203125" customWidth="1"/>
   </cols>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>• O nome da aba identifica a área (ex: "DevOps - Cloud", "PDV", "Redes")</v>
+        <v>• O nome da aba identifica a área no sistema (ex: "DevOps", "PDV", "Redes")</v>
       </c>
     </row>
     <row r="7">
@@ -2246,17 +2246,17 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>• Linha 1: Nome da área (será usado para identificar no sistema)</v>
+        <v>• Linha 1: Nome da área (importante para identificação)</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>• Linha 2: Mês/Ano de referência (ex: "Julho/2026", "Agosto/2026")</v>
+        <v>• Linha 2: Informativa (O Mês e Ano reais agora são selecionados na tela do sistema antes de importar!)</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>• Linha 3: Vazia (separador)</v>
+        <v>• Linha 3: Vazia (apenas para separação visual)</v>
       </c>
     </row>
     <row r="11">
@@ -2301,117 +2301,67 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>• Preencher com o horário do sobreaviso naquele dia</v>
+        <v>• Preencha com o horário do sobreaviso naquele dia</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>• Formatos aceitos:</v>
+        <v>• Formatos recomendados:</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v xml:space="preserve">    - "18:00-06:00" (horário início - horário fim)</v>
+        <v xml:space="preserve">    - "18:00-06:00" (horário de início e fim separados por hífen)</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v xml:space="preserve">    - "18:00 às 06:00" (com "às")</v>
+        <v xml:space="preserve">    - "24hs" ou "X" (para sinalizar um plantão de dia inteiro)</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v xml:space="preserve">    - "08:00-08:00" (turno de 24h)</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v xml:space="preserve">    - "24hs" ou "24h" (turno integral)</v>
+        <v xml:space="preserve">    - Deixe VAZIO se não houver plantão no dia</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v xml:space="preserve">    - "X" ou "S" (marca presença como 24h)</v>
+        <v>DICAS E REGRAS DA IMPORTAÇÃO:</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v xml:space="preserve">    - Vazio = sem plantão nesse dia</v>
+        <v>• SELECIONE O MÊS/ANO NO SISTEMA: A planilha será importada para o mês que você selecionar na tela de Importação.</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>• A importação substitui toda a escala do mês selecionado para aquela área.</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>REGRAS DE IMPORTAÇÃO:</v>
+        <v>• Plantonistas novos que não existiam no sistema serão criados automaticamente.</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>• A importação SUBSTITUI toda a escala do mês para a área</v>
+        <v>• Não proteja a planilha com senha, senão o sistema não conseguirá ler os dados.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>• Plantonistas novos são criados automaticamente (senha padrão: plantonista123)</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>• Plantonistas existentes são atualizados (cargo, contato)</v>
+        <v>• Múltiplas áreas podem ser importadas juntas, basta criar várias abas no mesmo arquivo Excel.</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>• Conflitos são detectados (mesmo plantonista em dois turnos sobrepostos)</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>• Níveis 2º, 3º, 4º não precisam ter dias preenchidos (são escalação fixa)</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>MÚLTIPLAS ÁREAS:</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>• Crie uma aba para cada área no mesmo arquivo</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>• Ou envie arquivos separados por área</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>DICAS:</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>• Não use proteção por senha no arquivo</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>• Aceita formatos .xlsx e .csv</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>• O sistema valida os dados antes de importar</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>• Veja a aba "DevOps - Cloud" como exemplo preenchido</v>
+        <v>👉 Veja a aba "DevOps - Cloud" neste arquivo como um exemplo prático já preenchido!</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A34"/>
   </ignoredErrors>
 </worksheet>
 </file>